--- a/artfynd/A 35131-2025 artfynd.xlsx
+++ b/artfynd/A 35131-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4037837</v>
+        <v>2852183</v>
       </c>
       <c r="B2" t="n">
-        <v>103249</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577843.6191059737</v>
+        <v>577844</v>
       </c>
       <c r="R2" t="n">
-        <v>6979554.817797404</v>
+        <v>6979555</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>1997-07-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1997-07-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2852183</v>
+        <v>4037837</v>
       </c>
       <c r="B3" t="n">
-        <v>96366</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577843.6191059737</v>
+        <v>577844</v>
       </c>
       <c r="R3" t="n">
-        <v>6979554.817797404</v>
+        <v>6979555</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,19 +858,9 @@
           <t>1997-07-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1997-07-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 35131-2025 artfynd.xlsx
+++ b/artfynd/A 35131-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2852183</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4037837</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>